--- a/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
+++ b/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
@@ -803,14 +803,14 @@
         <v>388869449010.67</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>1967876226.96</v>
+        <v>52456331446.13</v>
       </c>
       <c r="D5" s="9">
         <f>B5+C5</f>
         <v/>
       </c>
       <c r="E5" s="8" t="n">
-        <v>643970630739.3101</v>
+        <v>727158904358.71</v>
       </c>
       <c r="F5" s="8" t="n">
         <v>5995786999726.3</v>
@@ -833,14 +833,14 @@
         <v>405053833169.79</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>1805830468.76</v>
+        <v>52326423881.55</v>
       </c>
       <c r="D6" s="9">
         <f>B6+C6</f>
         <v/>
       </c>
       <c r="E6" s="8" t="n">
-        <v>630710707999.67</v>
+        <v>709027341688.51</v>
       </c>
       <c r="F6" s="8" t="n">
         <v>6269328000659.18</v>
@@ -863,14 +863,14 @@
         <v>431643439193.84</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>1941469270.79</v>
+        <v>54880868786.6</v>
       </c>
       <c r="D7" s="9">
         <f>B7+C7</f>
         <v/>
       </c>
       <c r="E7" s="8" t="n">
-        <v>652896822212.92</v>
+        <v>732613539836.0601</v>
       </c>
       <c r="F7" s="8" t="n">
         <v>6585479000139.78</v>
@@ -893,14 +893,14 @@
         <v>470938284813.26</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>2177284839.7</v>
+        <v>62298307526.46</v>
       </c>
       <c r="D8" s="9">
         <f>B8+C8</f>
         <v/>
       </c>
       <c r="E8" s="8" t="n">
-        <v>686702208869.38</v>
+        <v>773964691287.3</v>
       </c>
       <c r="F8" s="8" t="n">
         <v>7004140999893.37</v>

--- a/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
+++ b/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
@@ -521,14 +521,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estudo 11 — IBS total do Brasil, 2029-2033</t>
+          <t>Estudo 11: IBS total do Brasil, 2029-2033</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Série histórica (2015-2025) e projeção com PIB e inflação oficiais — memória de cálculo</t>
+          <t>Série histórica (2015-2025) e projeção com PIB e inflação oficiais, memória de cálculo</t>
         </is>
       </c>
     </row>
@@ -563,12 +563,12 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>Bolo total em 2033 (ICMS+ISS+IBS)</t>
+          <t>Arrecadação total em 2033 (ICMS+ISS+IBS)</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>R$ 1,608.6 bi (8.08% do PIB — mesma proporção de 2025, por premissa)</t>
+          <t>R$ 1,608.6 bi (8.08% do PIB, a mesma proporção de 2025, por premissa)</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Razão ICMS+ISS/PIB constante no nível de 2025 a partir de 2026 (elasticidade-PIB unitária) — mesma premissa de neutralidade de receita do art. 130 ADCT usada nos Estudos 06 e 09 do site.</t>
+          <t>A arrecadação de ICMS e ISS, como proporção do PIB (a carga tributária), é mantida constante no nível de 2025 a partir de 2026: ela cresce sempre no mesmo ritmo da economia, nem mais nem menos rápido. É o próprio desenho legal da transição para o IBS (art. 130, caput e §3º, IV, do ADCT: o Senado fixa a alíquota de referência do IBS para manter a Receita-Base dos Entes Subnacionais como proporção do PIB).</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>IFI — Instituição Fiscal Independente (Senado Federal), Relatório de Acompanhamento Fiscal (RAF) nº 107, 18/dez/2025: PIB real 2,2% a.a. (2027-2035), IPCA convergindo a 3,0% (centro da meta contínua).</t>
+          <t>IFI, Instituição Fiscal Independente (Senado Federal), Relatório de Acompanhamento Fiscal (RAF) nº 107, 18/dez/2025: PIB real 2,2% a.a. (2027-2035), IPCA convergindo a 3,0% (centro da meta contínua).</t>
         </is>
       </c>
     </row>
@@ -620,7 +620,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>SICONFI/STN — RREO Anexo 3 (2015-2018) e DCA Anexo I-C (2019-2025).</t>
+          <t>SICONFI/STN, RREO Anexo 3 (2015-2018) e DCA Anexo I-C (2019-2025).</t>
         </is>
       </c>
     </row>
@@ -632,7 +632,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SICONFI/STN — DCA Anexo I-C, todos os municípios brasileiros (2015-2025).</t>
+          <t>SICONFI/STN, DCA Anexo I-C, todos os municípios brasileiros (2015-2025).</t>
         </is>
       </c>
     </row>
@@ -656,7 +656,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Idêntico ao usado no Estudo 06 (Projeção ICMS/IBS por Estado, 2029-2033).</t>
+          <t>Fração remanescente de ICMS/ISS (f_a) e fração já convertida em IBS (s_a=1-f_a) a cada ano da transição, conforme ADCT arts. 128 e 131.</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Aba 'Série histórica': dados de entrada SICONFI 2015-2025. Aba 'Premissas macro': dados de entrada Focus/IFI 2026-2033. Aba 'PIB projetado': fórmulas que compõem o PIB nominal ano a ano. Aba 'Projeção IBS': fórmulas que aplicam a razão bolo/PIB e o cronograma ADCT — mude qualquer premissa nas abas de entrada (em azul) e a projeção recalcula.</t>
+          <t>Aba 'Série histórica': dados de entrada SICONFI 2015-2025. Aba 'Premissas macro': dados de entrada Focus/IFI 2026-2033. Aba 'PIB projetado': fórmulas que compõem o PIB nominal ano a ano. Aba 'Projeção IBS': fórmulas que aplicam a carga tributária constante e o cronograma ADCT. Mude qualquer premissa nas abas de entrada (em azul) e a projeção recalcula.</t>
         </is>
       </c>
     </row>
@@ -742,14 +742,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ICMS + ISS, Brasil — série histórica 2015-2025</t>
+          <t>ICMS + ISS, Brasil: série histórica 2015-2025</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dados de entrada (células em azul) — SICONFI/STN</t>
+          <t>Dados de entrada (células em azul), SICONFI/STN</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Dados de entrada (células em azul) — Boletim Focus (BCB) e IFI (RAF 107)</t>
+          <t>Dados de entrada (células em azul), Boletim Focus (BCB) e IFI (RAF 107)</t>
         </is>
       </c>
     </row>
@@ -1324,7 +1324,7 @@
     <row r="14" ht="55" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>2026-2030: mediana do Boletim Focus (BCB), consultada via API do Sistema de Expectativas de Mercado. 2031-2033: fora do horizonte do Focus (~5 anos); usa-se a projeção da IFI (RAF 107, 18/dez/2025), constante nos três anos por simplificação — a IFI projeta uma taxa média para 2027-2035, não ano a ano.</t>
+          <t>2026-2030: mediana do Boletim Focus (BCB), consultada via API do Sistema de Expectativas de Mercado. 2031-2033: fora do horizonte do Focus (~5 anos); usa-se a projeção da IFI (RAF 107, 18/dez/2025), constante nos três anos por simplificação, já que a IFI projeta uma taxa média para 2027-2035, não ano a ano.</t>
         </is>
       </c>
     </row>
@@ -1534,14 +1534,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fórmulas: Bolo(t) = (Bolo2025/PIB2025) × PIB(t); ICMS+ISS residual = Bolo × fa; IBS bruto = Bolo × sa</t>
+          <t>Fórmulas: Receita(t) = (Receita2025/PIB2025) × PIB(t); ICMS+ISS residual = Receita × fa; IBS bruto = Receita × sa</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Razão bolo/PIB em 2025 (base):</t>
+          <t>Carga tributária (arrecadação/PIB) em 2025, base da projeção:</t>
         </is>
       </c>
       <c r="B4" s="16">
@@ -1572,7 +1572,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Bolo projetado (R$)</t>
+          <t>Receita projetada (R$)</t>
         </is>
       </c>
       <c r="F6" s="6" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="H6" s="6" t="inlineStr">
         <is>
-          <t>Bolo / PIB</t>
+          <t>Carga tributária (% PIB)</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
     <row r="13" ht="55" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>f_a (fração remanescente de ICMS+ISS) e s_a=1-f_a (fração já convertida em IBS) seguem o cronograma da transição constitucional (ADCT arts. 128 e 131, LC 227/2026), idêntico ao usado no Estudo 06 (Projeção ICMS/IBS por Estado). "IBS bruto" não desconta a taxa do CGIBS nem a retenção do Seguro-Receita (ADCT art. 132), que incidem sobre a parcela distribuída aos entes pelo critério destino — não sobre o total nacional.</t>
+          <t>f_a (fração remanescente de ICMS+ISS) e s_a=1-f_a (fração já convertida em IBS) seguem o cronograma da transição constitucional (ADCT arts. 128 e 131, LC 227/2026). "IBS bruto" não desconta a taxa do CGIBS nem a retenção do Seguro-Receita (ADCT art. 132), que incidem sobre a parcela distribuída aos entes pelo critério destino, não sobre o total nacional.</t>
         </is>
       </c>
     </row>

--- a/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
+++ b/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="70">
   <si>
     <t xml:space="preserve">Estudo 11: IBS total do Brasil, 2029-2033</t>
   </si>
@@ -41,13 +41,13 @@
     <t xml:space="preserve">Resposta</t>
   </si>
   <si>
-    <t xml:space="preserve">IBS bruto nacional: de R$ 130.6 bi em 2029 a R$ 1,608.6 bi em 2033 (valores nominais).</t>
+    <t xml:space="preserve">IBS bruto nacional: de R$ 127.4 bi em 2029 a R$ 1,568.5 bi em 2033 (valores nominais).</t>
   </si>
   <si>
     <t xml:space="preserve">Arrecadação total em 2033 (ICMS+ISS+IBS)</t>
   </si>
   <si>
-    <t xml:space="preserve">R$ 1,608.6 bi (8.08% do PIB, a mesma proporção de 2025, por premissa)</t>
+    <t xml:space="preserve">R$ 1,568.5 bi (7.88% do PIB, a mesma proporção de 2025, por premissa)</t>
   </si>
   <si>
     <t xml:space="preserve">Premissa central</t>
@@ -185,10 +185,34 @@
     <t xml:space="preserve">Projeção do IBS total, Brasil, 2029-2033</t>
   </si>
   <si>
-    <t xml:space="preserve">Fórmulas: Receita(t) = (Receita2025/PIB2025) × PIB(t); ICMS+ISS residual = Receita × fa; IBS bruto = Receita × sa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Carga tributária (arrecadação/PIB) em 2025, base da projeção:</t>
+    <t xml:space="preserve">Fórmulas: Receita(t) = Razão(2024-2026) × PIB(t); ICMS+ISS residual = Receita × fa; IBS bruto = Receita × sa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Receita de referência (LC 214/2025, arts. 361-365): média da razão receita/PIB em 2024-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ICMS+ISS (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PIB (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Razão</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Situação</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fechado (DCA)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">estimativa preliminar (RREO 12m + PIB Focus)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Média 2024-2026 (usada na projeção)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O Teto de Referência do art. 130, §4º e §5º, do ADCT usa outro período (média 2012-2021) como salvaguarda, não como base de cálculo ano a ano da alíquota; não é usado nesta planilha.</t>
   </si>
   <si>
     <t xml:space="preserve">f_a (ICMS+ISS residual)</t>
@@ -222,7 +246,7 @@
     <numFmt numFmtId="166" formatCode="0.00%"/>
     <numFmt numFmtId="167" formatCode="\+0.00%;\-0.00%;0.00%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -306,8 +330,15 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10.5"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -318,6 +349,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1A3A5C"/>
         <bgColor rgb="FF333399"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEDF2F7"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -370,7 +407,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -435,7 +472,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -472,7 +517,7 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFEDF2F7"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
@@ -1682,7 +1727,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1715,217 +1760,322 @@
       <c r="F2" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="16" t="n">
-        <f aca="false">'Série histórica 2015-2025'!D15/'Série histórica 2015-2025'!F15</f>
-        <v>0.080823361105249</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="B4" s="16"/>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G6" s="6" t="s">
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="15" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B6" s="9" t="n">
+        <f aca="false">'Série histórica 2015-2025'!D14</f>
+        <v>954338315489.55</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <f aca="false">'Série histórica 2015-2025'!F14</f>
+        <v>11779250581628.3</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <f aca="false">B6/C6</f>
+        <v>0.0810185935748747</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>59</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="9" t="n">
+        <f aca="false">'Série histórica 2015-2025'!D15</f>
+        <v>1029573688573.62</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <f aca="false">'Série histórica 2015-2025'!F15</f>
+        <v>12738565613881.1</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <f aca="false">B7/C7</f>
+        <v>0.080823361105249</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B8" s="8" t="n">
+        <v>1018711484869.06</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>13656851382430.4</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <f aca="false">B8/C8</f>
+        <v>0.0745934371212123</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="18" t="n">
+        <f aca="false">AVERAGE(D6:D8)</f>
+        <v>0.078811797267112</v>
+      </c>
+      <c r="E9" s="14"/>
+    </row>
+    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="13" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="15" t="n">
         <v>2029</v>
       </c>
-      <c r="B7" s="17" t="n">
+      <c r="B14" s="19" t="n">
         <v>0.9</v>
       </c>
-      <c r="C7" s="10" t="n">
-        <f aca="false">1-B7</f>
+      <c r="C14" s="10" t="n">
+        <f aca="false">1-B14</f>
         <v>0.1</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D14" s="9" t="n">
         <f aca="false">'PIB projetado'!B9</f>
         <v>16163905249124.9</v>
       </c>
-      <c r="E7" s="9" t="n">
-        <f aca="false">$B$4*D7</f>
-        <v>1306421150821.05</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <f aca="false">E7*B7</f>
-        <v>1175779035738.95</v>
-      </c>
-      <c r="G7" s="9" t="n">
-        <f aca="false">E7*C7</f>
-        <v>130642115082.105</v>
-      </c>
-      <c r="H7" s="10" t="n">
-        <f aca="false">E7/D7</f>
-        <v>0.080823361105249</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="n">
+      <c r="E14" s="9" t="n">
+        <f aca="false">$D$9*D14</f>
+        <v>1273906423538.84</v>
+      </c>
+      <c r="F14" s="9" t="n">
+        <f aca="false">E14*B14</f>
+        <v>1146515781184.96</v>
+      </c>
+      <c r="G14" s="9" t="n">
+        <f aca="false">E14*C14</f>
+        <v>127390642353.884</v>
+      </c>
+      <c r="H14" s="10" t="n">
+        <f aca="false">E14/D14</f>
+        <v>0.078811797267112</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="15" t="n">
         <v>2030</v>
       </c>
-      <c r="B8" s="17" t="n">
+      <c r="B15" s="19" t="n">
         <v>0.8</v>
       </c>
-      <c r="C8" s="10" t="n">
-        <f aca="false">1-B8</f>
+      <c r="C15" s="10" t="n">
+        <f aca="false">1-B15</f>
         <v>0.2</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D15" s="9" t="n">
         <f aca="false">'PIB projetado'!B10</f>
         <v>17064234771501.2</v>
       </c>
-      <c r="E8" s="9" t="n">
-        <f aca="false">$B$4*D8</f>
-        <v>1379188808921.79</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <f aca="false">E8*B8</f>
-        <v>1103351047137.43</v>
-      </c>
-      <c r="G8" s="9" t="n">
-        <f aca="false">E8*C8</f>
-        <v>275837761784.357</v>
-      </c>
-      <c r="H8" s="10" t="n">
-        <f aca="false">E8/D8</f>
-        <v>0.080823361105249</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="n">
+      <c r="E15" s="9" t="n">
+        <f aca="false">$D$9*D15</f>
+        <v>1344863011329.95</v>
+      </c>
+      <c r="F15" s="9" t="n">
+        <f aca="false">E15*B15</f>
+        <v>1075890409063.96</v>
+      </c>
+      <c r="G15" s="9" t="n">
+        <f aca="false">E15*C15</f>
+        <v>268972602265.991</v>
+      </c>
+      <c r="H15" s="10" t="n">
+        <f aca="false">E15/D15</f>
+        <v>0.078811797267112</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="15" t="n">
         <v>2031</v>
       </c>
-      <c r="B9" s="17" t="n">
+      <c r="B16" s="19" t="n">
         <v>0.7</v>
       </c>
-      <c r="C9" s="10" t="n">
-        <f aca="false">1-B9</f>
+      <c r="C16" s="10" t="n">
+        <f aca="false">1-B16</f>
         <v>0.3</v>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D16" s="9" t="n">
         <f aca="false">'PIB projetado'!B11</f>
         <v>17962837374568.4</v>
       </c>
-      <c r="E9" s="9" t="n">
-        <f aca="false">$B$4*D9</f>
-        <v>1451816891599.61</v>
-      </c>
-      <c r="F9" s="9" t="n">
-        <f aca="false">E9*B9</f>
-        <v>1016271824119.72</v>
-      </c>
-      <c r="G9" s="9" t="n">
-        <f aca="false">E9*C9</f>
-        <v>435545067479.882</v>
-      </c>
-      <c r="H9" s="10" t="n">
-        <f aca="false">E9/D9</f>
-        <v>0.080823361105249</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="15" t="n">
+      <c r="E16" s="9" t="n">
+        <f aca="false">$D$9*D16</f>
+        <v>1415683497506.59</v>
+      </c>
+      <c r="F16" s="9" t="n">
+        <f aca="false">E16*B16</f>
+        <v>990978448254.612</v>
+      </c>
+      <c r="G16" s="9" t="n">
+        <f aca="false">E16*C16</f>
+        <v>424705049251.977</v>
+      </c>
+      <c r="H16" s="10" t="n">
+        <f aca="false">E16/D16</f>
+        <v>0.078811797267112</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="15" t="n">
         <v>2032</v>
       </c>
-      <c r="B10" s="17" t="n">
+      <c r="B17" s="19" t="n">
         <v>0.6</v>
       </c>
-      <c r="C10" s="10" t="n">
-        <f aca="false">1-B10</f>
+      <c r="C17" s="10" t="n">
+        <f aca="false">1-B17</f>
         <v>0.4</v>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D17" s="9" t="n">
         <f aca="false">'PIB projetado'!B12</f>
         <v>18908760390713.2</v>
       </c>
-      <c r="E10" s="9" t="n">
-        <f aca="false">$B$4*D10</f>
-        <v>1528269569111.24</v>
-      </c>
-      <c r="F10" s="9" t="n">
-        <f aca="false">E10*B10</f>
-        <v>916961741466.745</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <f aca="false">E10*C10</f>
-        <v>611307827644.497</v>
-      </c>
-      <c r="H10" s="10" t="n">
-        <f aca="false">E10/D10</f>
-        <v>0.080823361105249</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="15" t="n">
+      <c r="E17" s="9" t="n">
+        <f aca="false">$D$9*D17</f>
+        <v>1490233390485.29</v>
+      </c>
+      <c r="F17" s="9" t="n">
+        <f aca="false">E17*B17</f>
+        <v>894140034291.172</v>
+      </c>
+      <c r="G17" s="9" t="n">
+        <f aca="false">E17*C17</f>
+        <v>596093356194.115</v>
+      </c>
+      <c r="H17" s="10" t="n">
+        <f aca="false">E17/D17</f>
+        <v>0.078811797267112</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="15" t="n">
         <v>2033</v>
       </c>
-      <c r="B11" s="17" t="n">
+      <c r="B18" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="C11" s="10" t="n">
-        <f aca="false">1-B11</f>
+      <c r="C18" s="10" t="n">
+        <f aca="false">1-B18</f>
         <v>1</v>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D18" s="9" t="n">
         <f aca="false">'PIB projetado'!B13</f>
         <v>19904495712888.2</v>
       </c>
-      <c r="E11" s="9" t="n">
-        <f aca="false">$B$4*D11</f>
-        <v>1608748244620.64</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <f aca="false">E11*B11</f>
+      <c r="E18" s="9" t="n">
+        <f aca="false">$D$9*D18</f>
+        <v>1568709080828.24</v>
+      </c>
+      <c r="F18" s="9" t="n">
+        <f aca="false">E18*B18</f>
         <v>0</v>
       </c>
-      <c r="G11" s="9" t="n">
-        <f aca="false">E11*C11</f>
-        <v>1608748244620.64</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <f aca="false">E11/D11</f>
-        <v>0.080823361105249</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12"/>
-      <c r="H13" s="12"/>
+      <c r="G18" s="9" t="n">
+        <f aca="false">E18*C18</f>
+        <v>1568709080828.24</v>
+      </c>
+      <c r="H18" s="10" t="n">
+        <f aca="false">E18/D18</f>
+        <v>0.078811797267112</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="6">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A20:H20"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
+++ b/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
@@ -101,7 +101,7 @@
     <t xml:space="preserve">Gerado em</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-31</t>
+    <t xml:space="preserve">2026-08-01</t>
   </si>
   <si>
     <t xml:space="preserve">Página do estudo</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">Média 2024-2026 (usada na projeção)</t>
   </si>
   <si>
-    <t xml:space="preserve">O Teto de Referência do art. 130, §4º e §5º, do ADCT usa outro período (média 2012-2021) como salvaguarda, não como base de cálculo ano a ano da alíquota; não é usado nesta planilha.</t>
+    <t xml:space="preserve">O Teto de Referência (ADCT art. 130, §4º e §5º) compara a média 2029-2033 de CBS+Imposto Seletivo+IBS com a média 2012-2021 de IPI+ICMS+ISS+PIS/Cofins+IOF-seguros. Não altera os valores desta planilha: mesmo se ultrapassado, a redução só vale a partir de 2035 (fora desta projeção), e exige dados federais fora do escopo deste estudo (só ICMS/ISS/IBS).</t>
   </si>
   <si>
     <t xml:space="preserve">f_a (ICMS+ISS residual)</t>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="E9" s="14"/>
     </row>
-    <row r="11" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
         <v>62</v>
       </c>

--- a/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
+++ b/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
@@ -9,7 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Síntese" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Série histórica 2015-2025" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Série histórica 2013-2025" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Premissas macro 2026-2033" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="PIB projetado" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="Projeção IBS 2029-2033" sheetId="5" state="visible" r:id="rId7"/>
@@ -24,12 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
   <si>
     <t xml:space="preserve">Estudo 11: IBS total do Brasil, 2029-2033</t>
   </si>
   <si>
-    <t xml:space="preserve">Série histórica (2015-2025) e projeção com PIB e inflação oficiais, memória de cálculo</t>
+    <t xml:space="preserve">Série histórica (2013-2025) e projeção com PIB e inflação oficiais, memória de cálculo</t>
   </si>
   <si>
     <t xml:space="preserve">Pergunta</t>
@@ -71,13 +71,13 @@
     <t xml:space="preserve">Fonte do ICMS</t>
   </si>
   <si>
-    <t xml:space="preserve">SICONFI/STN, RREO Anexo 3 (2015-2018) e DCA Anexo I-C (2019-2025).</t>
+    <t xml:space="preserve">SICONFI/STN, DCA Anexo I-C (2013-2025), comparado com o RREO Anexo 3 para 2015-2018 (diferença &lt; 1,3%).</t>
   </si>
   <si>
     <t xml:space="preserve">Fonte do ISS</t>
   </si>
   <si>
-    <t xml:space="preserve">SICONFI/STN, DCA Anexo I-C, todos os municípios brasileiros (2015-2025).</t>
+    <t xml:space="preserve">SICONFI/STN, DCA Anexo I-C, todos os municípios brasileiros (2013-2025).</t>
   </si>
   <si>
     <t xml:space="preserve">Base legal da transição</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">O que este arquivo mostra</t>
   </si>
   <si>
-    <t xml:space="preserve">Aba 'Série histórica': dados de entrada SICONFI 2015-2025. Aba 'Premissas macro': dados de entrada Focus/IFI 2026-2033. Aba 'PIB projetado': fórmulas que compõem o PIB nominal ano a ano. Aba 'Projeção IBS': fórmulas que aplicam a carga tributária constante e o cronograma ADCT. Mude qualquer premissa nas abas de entrada (em azul) e a projeção recalcula.</t>
+    <t xml:space="preserve">Aba 'Série histórica': dados de entrada SICONFI 2013-2025. Aba 'Premissas macro': dados de entrada Focus/IFI 2026-2033. Aba 'PIB projetado': fórmulas que compõem o PIB nominal ano a ano. Aba 'Projeção IBS': fórmulas que aplicam a carga tributária constante e o cronograma ADCT. Mude qualquer premissa nas abas de entrada (em azul) e a projeção recalcula.</t>
   </si>
   <si>
     <t xml:space="preserve">Gerado em</t>
@@ -110,7 +110,7 @@
     <t xml:space="preserve">https://www.eduardoreisaraujo.com.br/estudos/ibs-projecao-nacional.html</t>
   </si>
   <si>
-    <t xml:space="preserve">ICMS + ISS, Brasil: série histórica 2015-2025</t>
+    <t xml:space="preserve">ICMS + ISS, Brasil: série histórica 2013-2025</t>
   </si>
   <si>
     <t xml:space="preserve">Dados de entrada (células em azul), SICONFI/STN</t>
@@ -140,13 +140,10 @@
     <t xml:space="preserve">Fonte ICMS</t>
   </si>
   <si>
-    <t xml:space="preserve">RREO</t>
-  </si>
-  <si>
     <t xml:space="preserve">DCA</t>
   </si>
   <si>
-    <t xml:space="preserve">ICMS 2015-2018: SICONFI/STN, RREO Anexo 3 (conta ICMSLiquidoExcetoTransferenciasEFUNDEB, coluna "TOTAL últimos 12 meses"). ICMS 2019-2025 e ISS 2015-2025: SICONFI/STN, DCA Anexo I-C. Fontes RREO e DCA convergem para o ICMS (diferença &lt; 1%).</t>
+    <t xml:space="preserve">ICMS e ISS 2013-2025: SICONFI/STN, DCA Anexo I-C, todos os estados e municípios. O SICONFI não publica o DCA antes de 2013. Para 2015-2018, o ICMS do DCA foi comparado com o RREO Anexo 3 (conta ICMSLiquidoExcetoTransferenciasEFUNDEB, coluna "TOTAL últimos 12 meses"): diferença &lt; 1,3% em todos os anos.</t>
   </si>
   <si>
     <t xml:space="preserve">Crescimento do PIB e inflação, 2026-2033</t>
@@ -974,7 +971,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1033,27 +1030,27 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="n">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B5" s="8" t="n">
-        <v>388869449010.67</v>
+        <v>351208258415.59</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>52456331446.13</v>
+        <v>44603470588.89</v>
       </c>
       <c r="D5" s="9" t="n">
         <f aca="false">B5+C5</f>
-        <v>441325780456.8</v>
+        <v>395811729004.48</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>727158904358.71</v>
+        <v>768024440131.99</v>
       </c>
       <c r="F5" s="8" t="n">
-        <v>5995786999726.3</v>
+        <v>5331618999627.08</v>
       </c>
       <c r="G5" s="10" t="n">
         <f aca="false">D5/F5</f>
-        <v>0.0736059804120703</v>
+        <v>0.0742385622513846</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>38</v>
@@ -1061,27 +1058,27 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="7" t="n">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B6" s="8" t="n">
-        <v>405053833169.79</v>
+        <v>374500455243.7</v>
       </c>
       <c r="C6" s="8" t="n">
-        <v>52326423881.55</v>
+        <v>48736779406.45</v>
       </c>
       <c r="D6" s="9" t="n">
         <f aca="false">B6+C6</f>
-        <v>457380257051.34</v>
+        <v>423237234650.15</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>709027341688.51</v>
+        <v>771787132328.83</v>
       </c>
       <c r="F6" s="8" t="n">
-        <v>6269328000659.18</v>
+        <v>5778953000008.59</v>
       </c>
       <c r="G6" s="10" t="n">
         <f aca="false">D6/F6</f>
-        <v>0.0729552285353788</v>
+        <v>0.0732377014745614</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>38</v>
@@ -1089,27 +1086,27 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="n">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>431643439193.84</v>
+        <v>385291418665.57</v>
       </c>
       <c r="C7" s="8" t="n">
-        <v>54880868786.6</v>
+        <v>52456331446.13</v>
       </c>
       <c r="D7" s="9" t="n">
         <f aca="false">B7+C7</f>
-        <v>486524307980.44</v>
+        <v>437747750111.7</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>732613539836.06</v>
+        <v>721263493891.62</v>
       </c>
       <c r="F7" s="8" t="n">
-        <v>6585479000139.78</v>
+        <v>5995786999726.3</v>
       </c>
       <c r="G7" s="10" t="n">
         <f aca="false">D7/F7</f>
-        <v>0.0738783477967378</v>
+        <v>0.0730092229980289</v>
       </c>
       <c r="H7" s="11" t="s">
         <v>38</v>
@@ -1117,27 +1114,27 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>470938284813.26</v>
+        <v>404214537044.43</v>
       </c>
       <c r="C8" s="8" t="n">
-        <v>62298307526.46</v>
+        <v>52326423881.55</v>
       </c>
       <c r="D8" s="9" t="n">
         <f aca="false">B8+C8</f>
-        <v>533236592339.72</v>
+        <v>456540960925.98</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>773964691287.3</v>
+        <v>707726271317.67</v>
       </c>
       <c r="F8" s="8" t="n">
-        <v>7004140999893.37</v>
+        <v>6269328000659.18</v>
       </c>
       <c r="G8" s="10" t="n">
         <f aca="false">D8/F8</f>
-        <v>0.0761316187592223</v>
+        <v>0.0728213551560833</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>38</v>
@@ -1145,217 +1142,273 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="7" t="n">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="B9" s="8" t="n">
-        <v>512501165557.69</v>
+        <v>437205536595.41</v>
       </c>
       <c r="C9" s="8" t="n">
-        <v>72575738376.57</v>
+        <v>54880868786.6</v>
       </c>
       <c r="D9" s="9" t="n">
         <f aca="false">B9+C9</f>
-        <v>585076903934.26</v>
+        <v>492086405382.01</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>814150513197.07</v>
+        <v>740989005972.98</v>
       </c>
       <c r="F9" s="8" t="n">
-        <v>7389130999453.28</v>
+        <v>6585479000139.78</v>
       </c>
       <c r="G9" s="10" t="n">
         <f aca="false">D9/F9</f>
-        <v>0.0791807458789876</v>
+        <v>0.0747229480758446</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="7" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B10" s="8" t="n">
-        <v>525280463571.25</v>
+        <v>472618579441.61</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>72939656553.14</v>
+        <v>62298307526.46</v>
       </c>
       <c r="D10" s="9" t="n">
         <f aca="false">B10+C10</f>
-        <v>598220120124.39</v>
+        <v>534916886968.07</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>796460803566.97</v>
+        <v>776403550007.77</v>
       </c>
       <c r="F10" s="8" t="n">
-        <v>7609597000575.82</v>
+        <v>7004140999893.37</v>
       </c>
       <c r="G10" s="10" t="n">
         <f aca="false">D10/F10</f>
-        <v>0.0786139029542724</v>
+        <v>0.076371518930903</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="7" t="n">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>655213422197.43</v>
+        <v>512501165557.69</v>
       </c>
       <c r="C11" s="8" t="n">
-        <v>90315695421.34</v>
+        <v>72575738376.57</v>
       </c>
       <c r="D11" s="9" t="n">
         <f aca="false">B11+C11</f>
-        <v>745529117618.77</v>
+        <v>585076903934.26</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>901850044265.15</v>
+        <v>814150513197.07</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>9012141999284.48</v>
+        <v>7389130999453.28</v>
       </c>
       <c r="G11" s="10" t="n">
         <f aca="false">D11/F11</f>
-        <v>0.0827249634635097</v>
+        <v>0.0791807458789876</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="7" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="B12" s="8" t="n">
-        <v>694424706419.7</v>
+        <v>525280463571.25</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>105738689405.94</v>
+        <v>72939656553.14</v>
       </c>
       <c r="D12" s="9" t="n">
         <f aca="false">B12+C12</f>
-        <v>800163395825.64</v>
+        <v>598220120124.39</v>
       </c>
       <c r="E12" s="8" t="n">
-        <v>915008144239.53</v>
+        <v>796460803566.97</v>
       </c>
       <c r="F12" s="8" t="n">
-        <v>10079676679176</v>
+        <v>7609597000575.82</v>
       </c>
       <c r="G12" s="10" t="n">
         <f aca="false">D12/F12</f>
-        <v>0.0793838355429325</v>
+        <v>0.0786139029542724</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="7" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="B13" s="8" t="n">
-        <v>708531573094.66</v>
+        <v>655213422197.43</v>
       </c>
       <c r="C13" s="8" t="n">
-        <v>120982841687.58</v>
+        <v>90315695421.34</v>
       </c>
       <c r="D13" s="9" t="n">
         <f aca="false">B13+C13</f>
-        <v>829514414782.24</v>
+        <v>745529117618.77</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>906673404756.58</v>
+        <v>901850044265.15</v>
       </c>
       <c r="F13" s="8" t="n">
-        <v>10943344667905</v>
+        <v>9012141999284.48</v>
       </c>
       <c r="G13" s="10" t="n">
         <f aca="false">D13/F13</f>
-        <v>0.0758008122704083</v>
+        <v>0.0827249634635097</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="7" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="B14" s="8" t="n">
-        <v>814527574371.58</v>
+        <v>694424706419.7</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>139810741117.97</v>
+        <v>105738689405.94</v>
       </c>
       <c r="D14" s="9" t="n">
         <f aca="false">B14+C14</f>
-        <v>954338315489.55</v>
+        <v>800163395825.64</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>995034974553.8</v>
+        <v>915008144239.53</v>
       </c>
       <c r="F14" s="8" t="n">
-        <v>11779250581628.3</v>
+        <v>10079676679176</v>
       </c>
       <c r="G14" s="10" t="n">
         <f aca="false">D14/F14</f>
-        <v>0.0810185935748747</v>
+        <v>0.0793838355429325</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="7" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="B15" s="8" t="n">
-        <v>875783701718.08</v>
+        <v>708531573094.66</v>
       </c>
       <c r="C15" s="8" t="n">
-        <v>153789986855.54</v>
+        <v>120982841687.58</v>
       </c>
       <c r="D15" s="9" t="n">
         <f aca="false">B15+C15</f>
-        <v>1029573688573.62</v>
+        <v>829514414782.24</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>1029573688573.62</v>
+        <v>906673404756.58</v>
       </c>
       <c r="F15" s="8" t="n">
-        <v>12738565613881.1</v>
+        <v>10943344667905</v>
       </c>
       <c r="G15" s="10" t="n">
         <f aca="false">D15/F15</f>
+        <v>0.0758008122704083</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>814527574371.58</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>139810741117.97</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <f aca="false">B16+C16</f>
+        <v>954338315489.55</v>
+      </c>
+      <c r="E16" s="8" t="n">
+        <v>995034974553.8</v>
+      </c>
+      <c r="F16" s="8" t="n">
+        <v>11779250581628.3</v>
+      </c>
+      <c r="G16" s="10" t="n">
+        <f aca="false">D16/F16</f>
+        <v>0.0810185935748747</v>
+      </c>
+      <c r="H16" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" s="8" t="n">
+        <v>875783701718.08</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>153789986855.54</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <f aca="false">B17+C17</f>
+        <v>1029573688573.62</v>
+      </c>
+      <c r="E17" s="8" t="n">
+        <v>1029573688573.62</v>
+      </c>
+      <c r="F17" s="8" t="n">
+        <v>12738565613881.1</v>
+      </c>
+      <c r="G17" s="10" t="n">
+        <f aca="false">D17/F17</f>
         <v>0.080823361105249</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H17" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="12" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="17" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A17:H17"/>
+    <mergeCell ref="A19:H19"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1382,7 +1435,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1392,7 +1445,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1405,13 +1458,13 @@
         <v>30</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="6" t="s">
         <v>44</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1425,7 +1478,7 @@
         <v>0.0512</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1439,7 +1492,7 @@
         <v>0.0422</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1453,7 +1506,7 @@
         <v>0.038</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1467,7 +1520,7 @@
         <v>0.035</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1481,7 +1534,7 @@
         <v>0.035</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1495,7 +1548,7 @@
         <v>0.03</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1509,7 +1562,7 @@
         <v>0.03</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1523,12 +1576,12 @@
         <v>0.03</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -1565,7 +1618,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1575,7 +1628,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1591,7 +1644,7 @@
         <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1741,7 +1794,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1751,7 +1804,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1761,7 +1814,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -1776,16 +1829,16 @@
         <v>30</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="E5" s="6" t="s">
         <v>57</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1793,11 +1846,11 @@
         <v>2024</v>
       </c>
       <c r="B6" s="9" t="n">
-        <f aca="false">'Série histórica 2015-2025'!D14</f>
+        <f aca="false">'Série histórica 2013-2025'!D16</f>
         <v>954338315489.55</v>
       </c>
       <c r="C6" s="9" t="n">
-        <f aca="false">'Série histórica 2015-2025'!F14</f>
+        <f aca="false">'Série histórica 2013-2025'!F16</f>
         <v>11779250581628.3</v>
       </c>
       <c r="D6" s="10" t="n">
@@ -1805,7 +1858,7 @@
         <v>0.0810185935748747</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1813,11 +1866,11 @@
         <v>2025</v>
       </c>
       <c r="B7" s="9" t="n">
-        <f aca="false">'Série histórica 2015-2025'!D15</f>
+        <f aca="false">'Série histórica 2013-2025'!D17</f>
         <v>1029573688573.62</v>
       </c>
       <c r="C7" s="9" t="n">
-        <f aca="false">'Série histórica 2015-2025'!F15</f>
+        <f aca="false">'Série histórica 2013-2025'!F17</f>
         <v>12738565613881.1</v>
       </c>
       <c r="D7" s="10" t="n">
@@ -1825,7 +1878,7 @@
         <v>0.080823361105249</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1843,12 +1896,12 @@
         <v>0.0745934371212123</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -1860,7 +1913,7 @@
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1875,25 +1928,25 @@
         <v>30</v>
       </c>
       <c r="B13" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>63</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>64</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>35</v>
       </c>
       <c r="E13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="H13" s="6" t="s">
         <v>67</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2058,7 +2111,7 @@
     </row>
     <row r="20" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>

--- a/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
+++ b/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="81">
   <si>
     <t xml:space="preserve">Estudo 11: IBS total do Brasil, 2029-2033</t>
   </si>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">Base legal da transição</t>
   </si>
   <si>
-    <t xml:space="preserve">ADCT arts. 128, 130 e 131 (EC 132/2023); LC 227/2026, art. 51 (CGIBS); ADCT art. 132 (Seguro-Receita).</t>
+    <t xml:space="preserve">ADCT arts. 128, 130, 131 e 132 (EC 132/2023); LC 227/2026, arts. 51 e 114 a 116 (CGIBS e critério histórico/destino).</t>
   </si>
   <si>
     <t xml:space="preserve">Cronograma f_a/s_a</t>
@@ -92,16 +92,22 @@
     <t xml:space="preserve">Fração remanescente de ICMS/ISS (f_a) e fração já convertida em IBS (s_a=1-f_a) a cada ano da transição, conforme ADCT arts. 128 e 131.</t>
   </si>
   <si>
+    <t xml:space="preserve">Divisão do IBS bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fração alpha_a distribuída pelo critério histórico; o restante pelo critério destino, líquido do CGIBS (art. 51 LC 227/2026) e do Seguro-Receita (5%, ADCT art. 132). Mesmos parâmetros já publicados no Estudo 06, usados aqui só para o agregado nacional (aba 'Projeção IBS 2029-2033').</t>
+  </si>
+  <si>
     <t xml:space="preserve">O que este arquivo mostra</t>
   </si>
   <si>
-    <t xml:space="preserve">Aba 'Série histórica': dados de entrada SICONFI 2013-2025. Aba 'Premissas macro': dados de entrada Focus/IFI 2026-2033. Aba 'PIB projetado': fórmulas que compõem o PIB nominal ano a ano. Aba 'Projeção IBS': fórmulas que aplicam a carga tributária constante e o cronograma ADCT. Mude qualquer premissa nas abas de entrada (em azul) e a projeção recalcula.</t>
+    <t xml:space="preserve">Aba 'Série histórica': dados de entrada SICONFI 2013-2025. Aba 'Premissas macro': dados de entrada Focus/IFI 2026-2033. Aba 'PIB projetado': fórmulas que compõem o PIB nominal ano a ano. Aba 'Projeção IBS': fórmulas que aplicam a carga tributária constante, o cronograma ADCT e a divisão do IBS bruto. Mude qualquer premissa nas abas de entrada (em azul) e a projeção recalcula.</t>
   </si>
   <si>
     <t xml:space="preserve">Gerado em</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-01</t>
+    <t xml:space="preserve">2026-08-02</t>
   </si>
   <si>
     <t xml:space="preserve">Página do estudo</t>
@@ -230,7 +236,37 @@
     <t xml:space="preserve">Carga tributária (% PIB)</t>
   </si>
   <si>
-    <t xml:space="preserve">f_a (fração remanescente de ICMS+ISS) e s_a=1-f_a (fração já convertida em IBS) seguem o cronograma da transição constitucional (ADCT arts. 128 e 131, LC 227/2026). "IBS bruto" não desconta a taxa do CGIBS nem a retenção do Seguro-Receita (ADCT art. 132), que incidem sobre a parcela distribuída aos entes pelo critério destino, não sobre o total nacional.</t>
+    <t xml:space="preserve">f_a (fração remanescente de ICMS+ISS) e s_a=1-f_a (fração já convertida em IBS) seguem o cronograma da transição constitucional (ADCT arts. 128 e 131, LC 227/2026). "IBS bruto" é a arrecadação total antes de qualquer dedução; a divisão entre critério histórico, critério destino, CGIBS e Seguro-Receita está na seção abaixo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão do IBS bruto (ADCT arts. 131-132; LC 227/2026 arts. 51 e 114-116): mesmos parâmetros alpha_a e c_a do Estudo 06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha_a (histórico)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_a (CGIBS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rho (Seguro-Receita)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBS histórico (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGIBS (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguro-Receita (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBS destino, líquido (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total (confere IBS bruto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha_a = fração do IBS bruto distribuída pelo critério histórico; (1-alpha_a) vai pelo critério destino, mas antes sofre duas deduções, nesta ordem: c_a (CGIBS, art. 51 LC 227/2026) e rho=5% (Seguro-Receita, ADCT art. 132). As quatro colunas de reais somam exatamente o IBS bruto do ano (coluna "Total" confere isso). alpha_a e c_a são os mesmos parâmetros já publicados no Estudo 06 (estudos/ibs-projecao-arrecadacao-br.html), usados aqui só para mostrar o tamanho de cada fatia no agregado nacional, sem entrar em qual estado ou município recebe o quê.</t>
   </si>
 </sst>
 </file>
@@ -737,7 +773,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -936,8 +972,20 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B4:F4"/>
@@ -955,6 +1003,7 @@
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -984,7 +1033,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -994,7 +1043,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1004,28 +1053,28 @@
     </row>
     <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1053,7 +1102,7 @@
         <v>0.0742385622513846</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1081,7 +1130,7 @@
         <v>0.0732377014745614</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1109,7 +1158,7 @@
         <v>0.0730092229980289</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1137,7 +1186,7 @@
         <v>0.0728213551560833</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1165,7 +1214,7 @@
         <v>0.0747229480758446</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1193,7 +1242,7 @@
         <v>0.076371518930903</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1221,7 +1270,7 @@
         <v>0.0791807458789876</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1249,7 +1298,7 @@
         <v>0.0786139029542724</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1277,7 +1326,7 @@
         <v>0.0827249634635097</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1305,7 +1354,7 @@
         <v>0.0793838355429325</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1333,7 +1382,7 @@
         <v>0.0758008122704083</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1361,7 +1410,7 @@
         <v>0.0810185935748747</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1389,12 +1438,12 @@
         <v>0.080823361105249</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -1435,7 +1484,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1445,7 +1494,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1455,16 +1504,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1478,7 +1527,7 @@
         <v>0.0512</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1492,7 +1541,7 @@
         <v>0.0422</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1506,7 +1555,7 @@
         <v>0.038</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1520,7 +1569,7 @@
         <v>0.035</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1534,7 +1583,7 @@
         <v>0.035</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1548,7 +1597,7 @@
         <v>0.03</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1562,7 +1611,7 @@
         <v>0.03</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1576,12 +1625,12 @@
         <v>0.03</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -1618,7 +1667,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1628,7 +1677,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1638,13 +1687,13 @@
     </row>
     <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1780,7 +1829,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1790,11 +1839,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1804,7 +1854,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1814,7 +1864,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -1826,19 +1876,19 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1858,7 +1908,7 @@
         <v>0.0810185935748747</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1878,7 +1928,7 @@
         <v>0.080823361105249</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1896,12 +1946,12 @@
         <v>0.0745934371212123</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
@@ -1913,7 +1963,7 @@
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1925,28 +1975,28 @@
     </row>
     <row r="13" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2109,9 +2159,9 @@
         <v>0.078811797267112</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -2121,14 +2171,241 @@
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
     </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+    </row>
+    <row r="23" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <f aca="false">G14*B24</f>
+        <v>101912513883.107</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <f aca="false">G14*(1-B24)*C24</f>
+        <v>509562569.415536</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <f aca="false">G14*(1-B24)*(1-C24)*D24</f>
+        <v>1248428295.06806</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <f aca="false">G14*(1-B24)*(1-C24)*(1-D24)</f>
+        <v>23720137606.2932</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <f aca="false">E24+F24+G24+H24</f>
+        <v>127390642353.884</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <f aca="false">G15*B25</f>
+        <v>215178081812.793</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <f aca="false">G15*(1-B25)*C25</f>
+        <v>537945204.531981</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <f aca="false">G15*(1-B25)*(1-C25)*D25</f>
+        <v>2662828762.43331</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <f aca="false">G15*(1-B25)*(1-C25)*(1-D25)</f>
+        <v>50593746486.2328</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <f aca="false">E25+F25+G25+H25</f>
+        <v>268972602265.991</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <f aca="false">G16*B26</f>
+        <v>339764039401.582</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <f aca="false">G16*(1-B26)*C26</f>
+        <v>569104765.997649</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <f aca="false">G16*(1-B26)*(1-C26)*D26</f>
+        <v>4218595254.21989</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <f aca="false">G16*(1-B26)*(1-C26)*(1-D26)</f>
+        <v>80153309830.1778</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <f aca="false">E26+F26+G26+H26</f>
+        <v>424705049251.977</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <f aca="false">G17*B27</f>
+        <v>476874684955.292</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <f aca="false">G17*(1-B27)*C27</f>
+        <v>596093356.194114</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <f aca="false">G17*(1-B27)*(1-C27)*D27</f>
+        <v>5931128894.13144</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <f aca="false">G17*(1-B27)*(1-C27)*(1-D27)</f>
+        <v>112691448988.497</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <f aca="false">E27+F27+G27+H27</f>
+        <v>596093356194.115</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <f aca="false">G18*B28</f>
+        <v>1411838172745.42</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <f aca="false">G18*(1-B28)*C28</f>
+        <v>784354540.414121</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <f aca="false">G18*(1-B28)*(1-C28)*D28</f>
+        <v>7804327677.1205</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <f aca="false">G18*(1-B28)*(1-C28)*(1-D28)</f>
+        <v>148282225865.289</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <f aca="false">E28+F28+G28+H28</f>
+        <v>1568709080828.24</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A30:I30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
+++ b/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="84">
   <si>
     <t xml:space="preserve">Estudo 11: IBS total do Brasil, 2029-2033</t>
   </si>
@@ -41,19 +41,19 @@
     <t xml:space="preserve">Resposta</t>
   </si>
   <si>
-    <t xml:space="preserve">IBS bruto nacional: de R$ 127.4 bi em 2029 a R$ 1,568.5 bi em 2033 (valores nominais).</t>
+    <t xml:space="preserve">IBS bruto nacional: de R$ 129.1 bi em 2029 a R$ 1,590.3 bi em 2033 (valores nominais).</t>
   </si>
   <si>
     <t xml:space="preserve">Arrecadação total em 2033 (ICMS+ISS+IBS)</t>
   </si>
   <si>
-    <t xml:space="preserve">R$ 1,568.5 bi (7.88% do PIB, a mesma proporção de 2025, por premissa)</t>
+    <t xml:space="preserve">R$ 1,590.3 bi (7.99% do PIB, a mesma proporção de 2025, por premissa)</t>
   </si>
   <si>
     <t xml:space="preserve">Premissa central</t>
   </si>
   <si>
-    <t xml:space="preserve">A arrecadação de ICMS e ISS, como proporção do PIB (a carga tributária), é mantida constante no nível de 2025 a partir de 2026: ela cresce sempre no mesmo ritmo da economia, nem mais nem menos rápido. É o próprio desenho legal da transição para o IBS (art. 130, caput e §3º, IV, do ADCT: o Senado fixa a alíquota de referência do IBS para manter a Receita-Base dos Entes Subnacionais como proporção do PIB).</t>
+    <t xml:space="preserve">A receita de referência (ICMS+ISS+FECOP), como proporção do PIB (a carga tributária), é mantida constante no nível médio de 2024-2026 a partir de 2027: ela cresce sempre no mesmo ritmo da economia, nem mais nem menos rápido. É o próprio desenho legal da transição para o IBS (LC 214/2025, arts. 361 a 365, redação da LC 227/2026: o Senado fixa a alíquota de referência do IBS para manter essa razão constante).</t>
   </si>
   <si>
     <t xml:space="preserve">Fonte do PIB e inflação, 2026-2030</t>
@@ -80,10 +80,16 @@
     <t xml:space="preserve">SICONFI/STN, DCA Anexo I-C, todos os municípios brasileiros (2013-2025).</t>
   </si>
   <si>
+    <t xml:space="preserve">Fonte do FECOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SICONFI/STN, DCA Anexo I-C (2019-2025); zero em 2013-2018; 2026 usa o valor de 2025 como estimativa preliminar. Mesmo critério do coeficiente validado no Estudo 06.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Base legal da transição</t>
   </si>
   <si>
-    <t xml:space="preserve">ADCT arts. 128, 130 e 131 (EC 132/2023); LC 227/2026, art. 51 (CGIBS); ADCT art. 132 (Seguro-Receita).</t>
+    <t xml:space="preserve">ADCT arts. 128, 130, 131 e 132 (EC 132/2023); LC 227/2026, arts. 51 e 114 a 116 (CGIBS e critério histórico/destino).</t>
   </si>
   <si>
     <t xml:space="preserve">Cronograma f_a/s_a</t>
@@ -92,16 +98,22 @@
     <t xml:space="preserve">Fração remanescente de ICMS/ISS (f_a) e fração já convertida em IBS (s_a=1-f_a) a cada ano da transição, conforme ADCT arts. 128 e 131.</t>
   </si>
   <si>
+    <t xml:space="preserve">Divisão do IBS bruto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fração alpha_a distribuída pelo critério histórico; o restante pelo critério destino, líquido do CGIBS (art. 51 LC 227/2026) e do Seguro-Receita (5%, ADCT art. 132). Mesmos parâmetros já publicados no Estudo 06, usados aqui só para o agregado nacional (aba 'Projeção IBS 2029-2033').</t>
+  </si>
+  <si>
     <t xml:space="preserve">O que este arquivo mostra</t>
   </si>
   <si>
-    <t xml:space="preserve">Aba 'Série histórica': dados de entrada SICONFI 2013-2025. Aba 'Premissas macro': dados de entrada Focus/IFI 2026-2033. Aba 'PIB projetado': fórmulas que compõem o PIB nominal ano a ano. Aba 'Projeção IBS': fórmulas que aplicam a carga tributária constante e o cronograma ADCT. Mude qualquer premissa nas abas de entrada (em azul) e a projeção recalcula.</t>
+    <t xml:space="preserve">Aba 'Série histórica': dados de entrada SICONFI 2013-2025. Aba 'Premissas macro': dados de entrada Focus/IFI 2026-2033. Aba 'PIB projetado': fórmulas que compõem o PIB nominal ano a ano. Aba 'Projeção IBS': fórmulas que aplicam a carga tributária constante, o cronograma ADCT e a divisão do IBS bruto. Mude qualquer premissa nas abas de entrada (em azul) e a projeção recalcula.</t>
   </si>
   <si>
     <t xml:space="preserve">Gerado em</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-01</t>
+    <t xml:space="preserve">2026-08-02</t>
   </si>
   <si>
     <t xml:space="preserve">Página do estudo</t>
@@ -110,7 +122,7 @@
     <t xml:space="preserve">https://www.eduardoreisaraujo.com.br/estudos/ibs-projecao-nacional.html</t>
   </si>
   <si>
-    <t xml:space="preserve">ICMS + ISS, Brasil: série histórica 2013-2025</t>
+    <t xml:space="preserve">ICMS + ISS + FECOP, Brasil: série histórica 2013-2025</t>
   </si>
   <si>
     <t xml:space="preserve">Dados de entrada (células em azul), SICONFI/STN</t>
@@ -125,16 +137,19 @@
     <t xml:space="preserve">ISS (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">ICMS+ISS nominal (R$)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ICMS+ISS real, 2025 (R$)</t>
+    <t xml:space="preserve">FECOP (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total nominal (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total real, 2025 (R$)</t>
   </si>
   <si>
     <t xml:space="preserve">PIB nominal (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">ICMS+ISS / PIB</t>
+    <t xml:space="preserve">Total / PIB</t>
   </si>
   <si>
     <t xml:space="preserve">Fonte ICMS</t>
@@ -143,7 +158,7 @@
     <t xml:space="preserve">DCA</t>
   </si>
   <si>
-    <t xml:space="preserve">ICMS e ISS 2013-2025: SICONFI/STN, DCA Anexo I-C, todos os estados e municípios. O SICONFI não publica o DCA antes de 2013. Para 2015-2018, o ICMS do DCA foi comparado com o RREO Anexo 3 (conta ICMSLiquidoExcetoTransferenciasEFUNDEB, coluna "TOTAL últimos 12 meses"): diferença &lt; 1,3% em todos os anos.</t>
+    <t xml:space="preserve">ICMS e ISS 2013-2025, FECOP 2019-2025: SICONFI/STN, DCA Anexo I-C, todos os estados e municípios. O SICONFI não publica o DCA antes de 2013 (FECOP tratado como zero em 2013-2018, sem coleta equivalente via RREO). Para 2015-2018, o ICMS do DCA foi comparado com o RREO Anexo 3 (conta ICMSLiquidoExcetoTransferenciasEFUNDEB, coluna "TOTAL últimos 12 meses"): diferença &lt; 1,3% em todos os anos. FECOP incluído porque a legislação da reforma o trata como parte da base substituída pelo IBS nos estados que o cobram (mesmo critério do coeficiente validado no Estudo 06).</t>
   </si>
   <si>
     <t xml:space="preserve">Crescimento do PIB e inflação, 2026-2033</t>
@@ -188,7 +203,7 @@
     <t xml:space="preserve">Receita de referência (LC 214/2025, arts. 361-365): média da razão receita/PIB em 2024-2026</t>
   </si>
   <si>
-    <t xml:space="preserve">ICMS+ISS (R$)</t>
+    <t xml:space="preserve">ICMS+ISS+FECOP (R$)</t>
   </si>
   <si>
     <t xml:space="preserve">PIB (R$)</t>
@@ -230,7 +245,37 @@
     <t xml:space="preserve">Carga tributária (% PIB)</t>
   </si>
   <si>
-    <t xml:space="preserve">f_a (fração remanescente de ICMS+ISS) e s_a=1-f_a (fração já convertida em IBS) seguem o cronograma da transição constitucional (ADCT arts. 128 e 131, LC 227/2026). "IBS bruto" não desconta a taxa do CGIBS nem a retenção do Seguro-Receita (ADCT art. 132), que incidem sobre a parcela distribuída aos entes pelo critério destino, não sobre o total nacional.</t>
+    <t xml:space="preserve">f_a (fração remanescente de ICMS+ISS) e s_a=1-f_a (fração já convertida em IBS) seguem o cronograma da transição constitucional (ADCT arts. 128 e 131, LC 227/2026). "IBS bruto" é a arrecadação total antes de qualquer dedução; a divisão entre critério histórico, critério destino, CGIBS e Seguro-Receita está na seção abaixo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Divisão do IBS bruto (ADCT arts. 131-132; LC 227/2026 arts. 51 e 114-116): mesmos parâmetros alpha_a e c_a do Estudo 06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha_a (histórico)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c_a (CGIBS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rho (Seguro-Receita)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBS histórico (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CGIBS (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Seguro-Receita (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBS destino, líquido (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total (confere IBS bruto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alpha_a = fração do IBS bruto distribuída pelo critério histórico; (1-alpha_a) vai pelo critério destino, mas antes sofre duas deduções, nesta ordem: c_a (CGIBS, art. 51 LC 227/2026) e rho=5% (Seguro-Receita, ADCT art. 132). As quatro colunas de reais somam exatamente o IBS bruto do ano (coluna "Total" confere isso). alpha_a e c_a são os mesmos parâmetros já publicados no Estudo 06 (estudos/ibs-projecao-arrecadacao-br.html), usados aqui só para mostrar o tamanho de cada fatia no agregado nacional, sem entrar em qual estado ou município recebe o quê.</t>
   </si>
 </sst>
 </file>
@@ -737,7 +782,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -936,8 +981,32 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
     </row>
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+    </row>
+    <row r="20" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="19">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B4:F4"/>
@@ -955,6 +1024,8 @@
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="B17:F17"/>
     <mergeCell ref="B18:F18"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -971,20 +1042,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -994,7 +1066,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1002,30 +1074,33 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
     </row>
-    <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1038,22 +1113,25 @@
       <c r="C5" s="8" t="n">
         <v>44603470588.89</v>
       </c>
-      <c r="D5" s="9" t="n">
-        <f aca="false">B5+C5</f>
+      <c r="D5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <f aca="false">B5+C5+D5</f>
         <v>395811729004.48</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="F5" s="8" t="n">
         <v>768024440131.99</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="G5" s="8" t="n">
         <v>5331618999627.08</v>
       </c>
-      <c r="G5" s="10" t="n">
-        <f aca="false">D5/F5</f>
+      <c r="H5" s="10" t="n">
+        <f aca="false">E5/G5</f>
         <v>0.0742385622513846</v>
       </c>
-      <c r="H5" s="11" t="s">
-        <v>38</v>
+      <c r="I5" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1066,22 +1144,25 @@
       <c r="C6" s="8" t="n">
         <v>48736779406.45</v>
       </c>
-      <c r="D6" s="9" t="n">
-        <f aca="false">B6+C6</f>
+      <c r="D6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <f aca="false">B6+C6+D6</f>
         <v>423237234650.15</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="F6" s="8" t="n">
         <v>771787132328.83</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="G6" s="8" t="n">
         <v>5778953000008.59</v>
       </c>
-      <c r="G6" s="10" t="n">
-        <f aca="false">D6/F6</f>
+      <c r="H6" s="10" t="n">
+        <f aca="false">E6/G6</f>
         <v>0.0732377014745614</v>
       </c>
-      <c r="H6" s="11" t="s">
-        <v>38</v>
+      <c r="I6" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1094,22 +1175,25 @@
       <c r="C7" s="8" t="n">
         <v>52456331446.13</v>
       </c>
-      <c r="D7" s="9" t="n">
-        <f aca="false">B7+C7</f>
+      <c r="D7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <f aca="false">B7+C7+D7</f>
         <v>437747750111.7</v>
       </c>
-      <c r="E7" s="8" t="n">
+      <c r="F7" s="8" t="n">
         <v>721263493891.62</v>
       </c>
-      <c r="F7" s="8" t="n">
+      <c r="G7" s="8" t="n">
         <v>5995786999726.3</v>
       </c>
-      <c r="G7" s="10" t="n">
-        <f aca="false">D7/F7</f>
+      <c r="H7" s="10" t="n">
+        <f aca="false">E7/G7</f>
         <v>0.0730092229980289</v>
       </c>
-      <c r="H7" s="11" t="s">
-        <v>38</v>
+      <c r="I7" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1122,22 +1206,25 @@
       <c r="C8" s="8" t="n">
         <v>52326423881.55</v>
       </c>
-      <c r="D8" s="9" t="n">
-        <f aca="false">B8+C8</f>
+      <c r="D8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <f aca="false">B8+C8+D8</f>
         <v>456540960925.98</v>
       </c>
-      <c r="E8" s="8" t="n">
+      <c r="F8" s="8" t="n">
         <v>707726271317.67</v>
       </c>
-      <c r="F8" s="8" t="n">
+      <c r="G8" s="8" t="n">
         <v>6269328000659.18</v>
       </c>
-      <c r="G8" s="10" t="n">
-        <f aca="false">D8/F8</f>
+      <c r="H8" s="10" t="n">
+        <f aca="false">E8/G8</f>
         <v>0.0728213551560833</v>
       </c>
-      <c r="H8" s="11" t="s">
-        <v>38</v>
+      <c r="I8" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1150,22 +1237,25 @@
       <c r="C9" s="8" t="n">
         <v>54880868786.6</v>
       </c>
-      <c r="D9" s="9" t="n">
-        <f aca="false">B9+C9</f>
+      <c r="D9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <f aca="false">B9+C9+D9</f>
         <v>492086405382.01</v>
       </c>
-      <c r="E9" s="8" t="n">
+      <c r="F9" s="8" t="n">
         <v>740989005972.98</v>
       </c>
-      <c r="F9" s="8" t="n">
+      <c r="G9" s="8" t="n">
         <v>6585479000139.78</v>
       </c>
-      <c r="G9" s="10" t="n">
-        <f aca="false">D9/F9</f>
+      <c r="H9" s="10" t="n">
+        <f aca="false">E9/G9</f>
         <v>0.0747229480758446</v>
       </c>
-      <c r="H9" s="11" t="s">
-        <v>38</v>
+      <c r="I9" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1178,22 +1268,25 @@
       <c r="C10" s="8" t="n">
         <v>62298307526.46</v>
       </c>
-      <c r="D10" s="9" t="n">
-        <f aca="false">B10+C10</f>
+      <c r="D10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <f aca="false">B10+C10+D10</f>
         <v>534916886968.07</v>
       </c>
-      <c r="E10" s="8" t="n">
+      <c r="F10" s="8" t="n">
         <v>776403550007.77</v>
       </c>
-      <c r="F10" s="8" t="n">
+      <c r="G10" s="8" t="n">
         <v>7004140999893.37</v>
       </c>
-      <c r="G10" s="10" t="n">
-        <f aca="false">D10/F10</f>
+      <c r="H10" s="10" t="n">
+        <f aca="false">E10/G10</f>
         <v>0.076371518930903</v>
       </c>
-      <c r="H10" s="11" t="s">
-        <v>38</v>
+      <c r="I10" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1206,22 +1299,25 @@
       <c r="C11" s="8" t="n">
         <v>72575738376.57</v>
       </c>
-      <c r="D11" s="9" t="n">
-        <f aca="false">B11+C11</f>
-        <v>585076903934.26</v>
-      </c>
-      <c r="E11" s="8" t="n">
-        <v>814150513197.07</v>
+      <c r="D11" s="8" t="n">
+        <v>11699003388.68</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <f aca="false">B11+C11+D11</f>
+        <v>596775907322.94</v>
       </c>
       <c r="F11" s="8" t="n">
+        <v>830429996370.55</v>
+      </c>
+      <c r="G11" s="8" t="n">
         <v>7389130999453.28</v>
       </c>
-      <c r="G11" s="10" t="n">
-        <f aca="false">D11/F11</f>
-        <v>0.0791807458789876</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>38</v>
+      <c r="H11" s="10" t="n">
+        <f aca="false">E11/G11</f>
+        <v>0.0807640177670548</v>
+      </c>
+      <c r="I11" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1234,22 +1330,25 @@
       <c r="C12" s="8" t="n">
         <v>72939656553.14</v>
       </c>
-      <c r="D12" s="9" t="n">
-        <f aca="false">B12+C12</f>
-        <v>598220120124.39</v>
-      </c>
-      <c r="E12" s="8" t="n">
-        <v>796460803566.97</v>
+      <c r="D12" s="8" t="n">
+        <v>12775546215.27</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <f aca="false">B12+C12+D12</f>
+        <v>610995666339.66</v>
       </c>
       <c r="F12" s="8" t="n">
+        <v>813469963677.64</v>
+      </c>
+      <c r="G12" s="8" t="n">
         <v>7609597000575.82</v>
       </c>
-      <c r="G12" s="10" t="n">
-        <f aca="false">D12/F12</f>
-        <v>0.0786139029542724</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>38</v>
+      <c r="H12" s="10" t="n">
+        <f aca="false">E12/G12</f>
+        <v>0.080292775858357</v>
+      </c>
+      <c r="I12" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1262,22 +1361,25 @@
       <c r="C13" s="8" t="n">
         <v>90315695421.34</v>
       </c>
-      <c r="D13" s="9" t="n">
-        <f aca="false">B13+C13</f>
-        <v>745529117618.77</v>
-      </c>
-      <c r="E13" s="8" t="n">
-        <v>901850044265.15</v>
+      <c r="D13" s="8" t="n">
+        <v>15797405283.66</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <f aca="false">B13+C13+D13</f>
+        <v>761326522902.43</v>
       </c>
       <c r="F13" s="8" t="n">
+        <v>920959815188.44</v>
+      </c>
+      <c r="G13" s="8" t="n">
         <v>9012141999284.48</v>
       </c>
-      <c r="G13" s="10" t="n">
-        <f aca="false">D13/F13</f>
-        <v>0.0827249634635097</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>38</v>
+      <c r="H13" s="10" t="n">
+        <f aca="false">E13/G13</f>
+        <v>0.0844778658572929</v>
+      </c>
+      <c r="I13" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1290,22 +1392,25 @@
       <c r="C14" s="8" t="n">
         <v>105738689405.94</v>
       </c>
-      <c r="D14" s="9" t="n">
-        <f aca="false">B14+C14</f>
-        <v>800163395825.64</v>
-      </c>
-      <c r="E14" s="8" t="n">
-        <v>915008144239.53</v>
+      <c r="D14" s="8" t="n">
+        <v>14732300782.29</v>
+      </c>
+      <c r="E14" s="9" t="n">
+        <f aca="false">B14+C14+D14</f>
+        <v>814895696607.93</v>
       </c>
       <c r="F14" s="8" t="n">
+        <v>931854922371.98</v>
+      </c>
+      <c r="G14" s="8" t="n">
         <v>10079676679176</v>
       </c>
-      <c r="G14" s="10" t="n">
-        <f aca="false">D14/F14</f>
-        <v>0.0793838355429325</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>38</v>
+      <c r="H14" s="10" t="n">
+        <f aca="false">E14/G14</f>
+        <v>0.0808454201999807</v>
+      </c>
+      <c r="I14" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1318,22 +1423,25 @@
       <c r="C15" s="8" t="n">
         <v>120982841687.58</v>
       </c>
-      <c r="D15" s="9" t="n">
-        <f aca="false">B15+C15</f>
-        <v>829514414782.24</v>
-      </c>
-      <c r="E15" s="8" t="n">
-        <v>906673404756.58</v>
+      <c r="D15" s="8" t="n">
+        <v>12037722674.32</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <f aca="false">B15+C15+D15</f>
+        <v>841552137456.56</v>
       </c>
       <c r="F15" s="8" t="n">
+        <v>919830840972.45</v>
+      </c>
+      <c r="G15" s="8" t="n">
         <v>10943344667905</v>
       </c>
-      <c r="G15" s="10" t="n">
-        <f aca="false">D15/F15</f>
-        <v>0.0758008122704083</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>38</v>
+      <c r="H15" s="10" t="n">
+        <f aca="false">E15/G15</f>
+        <v>0.0769008162490479</v>
+      </c>
+      <c r="I15" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1346,22 +1454,25 @@
       <c r="C16" s="8" t="n">
         <v>139810741117.97</v>
       </c>
-      <c r="D16" s="9" t="n">
-        <f aca="false">B16+C16</f>
-        <v>954338315489.55</v>
-      </c>
-      <c r="E16" s="8" t="n">
-        <v>995034974553.8</v>
+      <c r="D16" s="8" t="n">
+        <v>13618393510.28</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <f aca="false">B16+C16+D16</f>
+        <v>967956708999.83</v>
       </c>
       <c r="F16" s="8" t="n">
+        <v>1009234108781.18</v>
+      </c>
+      <c r="G16" s="8" t="n">
         <v>11779250581628.3</v>
       </c>
-      <c r="G16" s="10" t="n">
-        <f aca="false">D16/F16</f>
-        <v>0.0810185935748747</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>38</v>
+      <c r="H16" s="10" t="n">
+        <f aca="false">E16/G16</f>
+        <v>0.0821747276952847</v>
+      </c>
+      <c r="I16" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1374,27 +1485,30 @@
       <c r="C17" s="8" t="n">
         <v>153789986855.54</v>
       </c>
-      <c r="D17" s="9" t="n">
-        <f aca="false">B17+C17</f>
-        <v>1029573688573.62</v>
-      </c>
-      <c r="E17" s="8" t="n">
-        <v>1029573688573.62</v>
+      <c r="D17" s="8" t="n">
+        <v>13981757501.54</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <f aca="false">B17+C17+D17</f>
+        <v>1043555446075.16</v>
       </c>
       <c r="F17" s="8" t="n">
+        <v>1043555446075.16</v>
+      </c>
+      <c r="G17" s="8" t="n">
         <v>12738565613881.1</v>
       </c>
-      <c r="G17" s="10" t="n">
-        <f aca="false">D17/F17</f>
-        <v>0.080823361105249</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>38</v>
+      <c r="H17" s="10" t="n">
+        <f aca="false">E17/G17</f>
+        <v>0.0819209538739595</v>
+      </c>
+      <c r="I17" s="11" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="12" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B19" s="12"/>
       <c r="C19" s="12"/>
@@ -1403,12 +1517,13 @@
       <c r="F19" s="12"/>
       <c r="G19" s="12"/>
       <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A19:H19"/>
+    <mergeCell ref="A19:I19"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1435,7 +1550,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1445,7 +1560,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1455,16 +1570,16 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1478,7 +1593,7 @@
         <v>0.0512</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1492,7 +1607,7 @@
         <v>0.0422</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1506,7 +1621,7 @@
         <v>0.038</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1520,7 +1635,7 @@
         <v>0.035</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1534,7 +1649,7 @@
         <v>0.035</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1548,7 +1663,7 @@
         <v>0.03</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1562,7 +1677,7 @@
         <v>0.03</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1576,12 +1691,12 @@
         <v>0.03</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="12" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B14" s="12"/>
       <c r="C14" s="12"/>
@@ -1618,7 +1733,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1628,7 +1743,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1638,13 +1753,13 @@
     </row>
     <row r="4" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1780,7 +1895,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:I30"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="8"/>
@@ -1790,11 +1905,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="22"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1804,7 +1920,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1814,7 +1930,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="16" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B4" s="16"/>
       <c r="C4" s="16"/>
@@ -1824,21 +1940,21 @@
       <c r="G4" s="16"/>
       <c r="H4" s="16"/>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1846,19 +1962,19 @@
         <v>2024</v>
       </c>
       <c r="B6" s="9" t="n">
-        <f aca="false">'Série histórica 2013-2025'!D16</f>
-        <v>954338315489.55</v>
+        <f aca="false">'Série histórica 2013-2025'!E16</f>
+        <v>967956708999.83</v>
       </c>
       <c r="C6" s="9" t="n">
-        <f aca="false">'Série histórica 2013-2025'!F16</f>
+        <f aca="false">'Série histórica 2013-2025'!G16</f>
         <v>11779250581628.3</v>
       </c>
       <c r="D6" s="10" t="n">
         <f aca="false">B6/C6</f>
-        <v>0.0810185935748747</v>
+        <v>0.0821747276952847</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1866,19 +1982,19 @@
         <v>2025</v>
       </c>
       <c r="B7" s="9" t="n">
-        <f aca="false">'Série histórica 2013-2025'!D17</f>
-        <v>1029573688573.62</v>
+        <f aca="false">'Série histórica 2013-2025'!E17</f>
+        <v>1043555446075.16</v>
       </c>
       <c r="C7" s="9" t="n">
-        <f aca="false">'Série histórica 2013-2025'!F17</f>
+        <f aca="false">'Série histórica 2013-2025'!G17</f>
         <v>12738565613881.1</v>
       </c>
       <c r="D7" s="10" t="n">
         <f aca="false">B7/C7</f>
-        <v>0.080823361105249</v>
+        <v>0.0819209538739595</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1886,34 +2002,34 @@
         <v>2026</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1018711484869.06</v>
+        <v>1032693242370.6</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>13656851382430.4</v>
       </c>
       <c r="D8" s="10" t="n">
         <f aca="false">B8/C8</f>
-        <v>0.0745934371212123</v>
+        <v>0.0756172278259664</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="17" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="B9" s="17"/>
       <c r="C9" s="17"/>
       <c r="D9" s="18" t="n">
         <f aca="false">AVERAGE(D6:D8)</f>
-        <v>0.078811797267112</v>
+        <v>0.0799043031317369</v>
       </c>
       <c r="E9" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B11" s="12"/>
       <c r="C11" s="12"/>
@@ -1925,28 +2041,28 @@
     </row>
     <row r="13" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1966,19 +2082,19 @@
       </c>
       <c r="E14" s="9" t="n">
         <f aca="false">$D$9*D14</f>
-        <v>1273906423538.84</v>
+        <v>1291565584818.75</v>
       </c>
       <c r="F14" s="9" t="n">
         <f aca="false">E14*B14</f>
-        <v>1146515781184.96</v>
+        <v>1162409026336.87</v>
       </c>
       <c r="G14" s="9" t="n">
         <f aca="false">E14*C14</f>
-        <v>127390642353.884</v>
+        <v>129156558481.875</v>
       </c>
       <c r="H14" s="10" t="n">
         <f aca="false">E14/D14</f>
-        <v>0.078811797267112</v>
+        <v>0.0799043031317369</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1998,19 +2114,19 @@
       </c>
       <c r="E15" s="9" t="n">
         <f aca="false">$D$9*D15</f>
-        <v>1344863011329.95</v>
+        <v>1363505787893.15</v>
       </c>
       <c r="F15" s="9" t="n">
         <f aca="false">E15*B15</f>
-        <v>1075890409063.96</v>
+        <v>1090804630314.52</v>
       </c>
       <c r="G15" s="9" t="n">
         <f aca="false">E15*C15</f>
-        <v>268972602265.991</v>
+        <v>272701157578.631</v>
       </c>
       <c r="H15" s="10" t="n">
         <f aca="false">E15/D15</f>
-        <v>0.078811797267112</v>
+        <v>0.0799043031317369</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2030,19 +2146,19 @@
       </c>
       <c r="E16" s="9" t="n">
         <f aca="false">$D$9*D16</f>
-        <v>1415683497506.59</v>
+        <v>1435308002683.61</v>
       </c>
       <c r="F16" s="9" t="n">
         <f aca="false">E16*B16</f>
-        <v>990978448254.612</v>
+        <v>1004715601878.53</v>
       </c>
       <c r="G16" s="9" t="n">
         <f aca="false">E16*C16</f>
-        <v>424705049251.977</v>
+        <v>430592400805.082</v>
       </c>
       <c r="H16" s="10" t="n">
         <f aca="false">E16/D16</f>
-        <v>0.078811797267112</v>
+        <v>0.0799043031317369</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2062,19 +2178,19 @@
       </c>
       <c r="E17" s="9" t="n">
         <f aca="false">$D$9*D17</f>
-        <v>1490233390485.29</v>
+        <v>1510891322104.93</v>
       </c>
       <c r="F17" s="9" t="n">
         <f aca="false">E17*B17</f>
-        <v>894140034291.172</v>
+        <v>906534793262.956</v>
       </c>
       <c r="G17" s="9" t="n">
         <f aca="false">E17*C17</f>
-        <v>596093356194.115</v>
+        <v>604356528841.971</v>
       </c>
       <c r="H17" s="10" t="n">
         <f aca="false">E17/D17</f>
-        <v>0.078811797267112</v>
+        <v>0.0799043031317369</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2094,7 +2210,7 @@
       </c>
       <c r="E18" s="9" t="n">
         <f aca="false">$D$9*D18</f>
-        <v>1568709080828.24</v>
+        <v>1590454859126.97</v>
       </c>
       <c r="F18" s="9" t="n">
         <f aca="false">E18*B18</f>
@@ -2102,16 +2218,16 @@
       </c>
       <c r="G18" s="9" t="n">
         <f aca="false">E18*C18</f>
-        <v>1568709080828.24</v>
+        <v>1590454859126.97</v>
       </c>
       <c r="H18" s="10" t="n">
         <f aca="false">E18/D18</f>
-        <v>0.078811797267112</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="54.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+        <v>0.0799043031317369</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="12" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="12"/>
@@ -2121,14 +2237,241 @@
       <c r="G20" s="12"/>
       <c r="H20" s="12"/>
     </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+    </row>
+    <row r="23" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="15" t="n">
+        <v>2029</v>
+      </c>
+      <c r="B24" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C24" s="19" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="D24" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <f aca="false">G14*B24</f>
+        <v>103325246785.5</v>
+      </c>
+      <c r="F24" s="9" t="n">
+        <f aca="false">G14*(1-B24)*C24</f>
+        <v>516626233.9275</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <f aca="false">G14*(1-B24)*(1-C24)*D24</f>
+        <v>1265734273.12237</v>
+      </c>
+      <c r="H24" s="9" t="n">
+        <f aca="false">G14*(1-B24)*(1-C24)*(1-D24)</f>
+        <v>24048951189.3251</v>
+      </c>
+      <c r="I24" s="9" t="n">
+        <f aca="false">E24+F24+G24+H24</f>
+        <v>129156558481.875</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="15" t="n">
+        <v>2030</v>
+      </c>
+      <c r="B25" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C25" s="19" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="D25" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <f aca="false">G15*B25</f>
+        <v>218160926062.905</v>
+      </c>
+      <c r="F25" s="9" t="n">
+        <f aca="false">G15*(1-B25)*C25</f>
+        <v>545402315.157261</v>
+      </c>
+      <c r="G25" s="9" t="n">
+        <f aca="false">G15*(1-B25)*(1-C25)*D25</f>
+        <v>2699741460.02844</v>
+      </c>
+      <c r="H25" s="9" t="n">
+        <f aca="false">G15*(1-B25)*(1-C25)*(1-D25)</f>
+        <v>51295087740.5404</v>
+      </c>
+      <c r="I25" s="9" t="n">
+        <f aca="false">E25+F25+G25+H25</f>
+        <v>272701157578.631</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="15" t="n">
+        <v>2031</v>
+      </c>
+      <c r="B26" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C26" s="19" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="D26" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <f aca="false">G16*B26</f>
+        <v>344473920644.066</v>
+      </c>
+      <c r="F26" s="9" t="n">
+        <f aca="false">G16*(1-B26)*C26</f>
+        <v>576993817.07881</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <f aca="false">G16*(1-B26)*(1-C26)*D26</f>
+        <v>4277074317.19688</v>
+      </c>
+      <c r="H26" s="9" t="n">
+        <f aca="false">G16*(1-B26)*(1-C26)*(1-D26)</f>
+        <v>81264412026.7408</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <f aca="false">E26+F26+G26+H26</f>
+        <v>430592400805.082</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="15" t="n">
+        <v>2032</v>
+      </c>
+      <c r="B27" s="19" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="C27" s="19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D27" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E27" s="9" t="n">
+        <f aca="false">G17*B27</f>
+        <v>483485223073.577</v>
+      </c>
+      <c r="F27" s="9" t="n">
+        <f aca="false">G17*(1-B27)*C27</f>
+        <v>604356528.84197</v>
+      </c>
+      <c r="G27" s="9" t="n">
+        <f aca="false">G17*(1-B27)*(1-C27)*D27</f>
+        <v>6013347461.97761</v>
+      </c>
+      <c r="H27" s="9" t="n">
+        <f aca="false">G17*(1-B27)*(1-C27)*(1-D27)</f>
+        <v>114253601777.575</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <f aca="false">E27+F27+G27+H27</f>
+        <v>604356528841.971</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="15" t="n">
+        <v>2033</v>
+      </c>
+      <c r="B28" s="19" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="C28" s="19" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="D28" s="19" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E28" s="9" t="n">
+        <f aca="false">G18*B28</f>
+        <v>1431409373214.27</v>
+      </c>
+      <c r="F28" s="9" t="n">
+        <f aca="false">G18*(1-B28)*C28</f>
+        <v>795227429.563486</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <f aca="false">G18*(1-B28)*(1-C28)*D28</f>
+        <v>7912512924.15668</v>
+      </c>
+      <c r="H28" s="9" t="n">
+        <f aca="false">G18*(1-B28)*(1-C28)*(1-D28)</f>
+        <v>150337745558.977</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <f aca="false">E28+F28+G28+H28</f>
+        <v>1590454859126.97</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="64.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A9:C9"/>
     <mergeCell ref="A11:H11"/>
     <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A30:I30"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
+++ b/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
@@ -567,7 +567,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>IBS bruto nacional: de R$ 111.4 bi em 2029 a R$ 1,213.2 bi em 2033 (R$ constantes de 2025).</t>
+          <t>IBS bruto nacional: de R$ 109.7 bi em 2029 a R$ 1,194.4 bi em 2033 (R$ constantes de 2025).</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>R$ 1,213.2 bi (8.12% do PIB, a mesma proporção de 2025, por premissa)</t>
+          <t>R$ 1,194.4 bi (7.99% do PIB, a mesma proporção de 2025, por premissa)</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-09-07</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
         <v>2019</v>
       </c>
       <c r="B11" s="8" t="n">
-        <v>512501165557.69</v>
+        <v>499579904118.77</v>
       </c>
       <c r="C11" s="8" t="n">
         <v>72575738376.57001</v>
@@ -1054,7 +1054,7 @@
         <v/>
       </c>
       <c r="F11" s="8" t="n">
-        <v>830429996370.55</v>
+        <v>812449707692.41</v>
       </c>
       <c r="G11" s="8" t="n">
         <v>7389130999453.28</v>
@@ -1074,7 +1074,7 @@
         <v>2020</v>
       </c>
       <c r="B12" s="8" t="n">
-        <v>525280463571.25</v>
+        <v>510683536642.49</v>
       </c>
       <c r="C12" s="8" t="n">
         <v>72939656553.14</v>
@@ -1087,7 +1087,7 @@
         <v/>
       </c>
       <c r="F12" s="8" t="n">
-        <v>813469963677.64</v>
+        <v>794035846100.87</v>
       </c>
       <c r="G12" s="8" t="n">
         <v>7609597000575.82</v>
@@ -1107,7 +1107,7 @@
         <v>2021</v>
       </c>
       <c r="B13" s="8" t="n">
-        <v>655213422197.4301</v>
+        <v>642861083066.52</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>90315695421.34</v>
@@ -1120,7 +1120,7 @@
         <v/>
       </c>
       <c r="F13" s="8" t="n">
-        <v>920959815188.4399</v>
+        <v>906017464408.6801</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>9012141999284.48</v>
@@ -1140,7 +1140,7 @@
         <v>2022</v>
       </c>
       <c r="B14" s="8" t="n">
-        <v>694424706419.7</v>
+        <v>679688910408.1899</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>105738689405.94</v>
@@ -1153,7 +1153,7 @@
         <v/>
       </c>
       <c r="F14" s="8" t="n">
-        <v>931854922371.98</v>
+        <v>915004147351.87</v>
       </c>
       <c r="G14" s="8" t="n">
         <v>10079676679176</v>
@@ -1173,7 +1173,7 @@
         <v>2023</v>
       </c>
       <c r="B15" s="8" t="n">
-        <v>708531573094.66</v>
+        <v>690862487567.4301</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>120982841687.58</v>
@@ -1186,7 +1186,7 @@
         <v/>
       </c>
       <c r="F15" s="8" t="n">
-        <v>919830840972.45</v>
+        <v>900518229101.66</v>
       </c>
       <c r="G15" s="8" t="n">
         <v>10943344667905</v>
@@ -1206,7 +1206,7 @@
         <v>2024</v>
       </c>
       <c r="B16" s="8" t="n">
-        <v>814527574371.58</v>
+        <v>794639652610.3199</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>139810741117.97</v>
@@ -1219,7 +1219,7 @@
         <v/>
       </c>
       <c r="F16" s="8" t="n">
-        <v>1009234108781.18</v>
+        <v>988498089486.5</v>
       </c>
       <c r="G16" s="8" t="n">
         <v>11779250581628.3</v>
@@ -1239,7 +1239,7 @@
         <v>2025</v>
       </c>
       <c r="B17" s="8" t="n">
-        <v>875783701718.08</v>
+        <v>848995884628.38</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>153789986855.54</v>
@@ -1252,7 +1252,7 @@
         <v/>
       </c>
       <c r="F17" s="8" t="n">
-        <v>1043555446075.16</v>
+        <v>1016767628985.46</v>
       </c>
       <c r="G17" s="8" t="n">
         <v>12738565613881.1</v>
@@ -1764,7 +1764,7 @@
         <v>2026</v>
       </c>
       <c r="B8" s="8" t="n">
-        <v>1032976269845.68</v>
+        <v>1033149971592.79</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>12991145892873.13</v>
@@ -2207,7 +2207,7 @@
         <v>0.9</v>
       </c>
       <c r="C28" s="18" t="n">
-        <v>0.005</v>
+        <v>0.002</v>
       </c>
       <c r="D28" s="18" t="n">
         <v>0.05</v>

--- a/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
+++ b/materiais/ibs-projecao-nacional-memoria-calculo.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Fração alpha_a distribuída pelo critério histórico; o restante pelo critério destino, líquido do CGIBS (art. 51 LC 227/2026) e do Seguro-Receita (5%, ADCT art. 132). Mesmos parâmetros já publicados no Estudo 06, usados aqui só para o agregado nacional (aba 'Projeção IBS 2029-2033').</t>
+          <t>Fração alpha_a distribuída pelo critério histórico; o restante pelo critério destino, líquido do Seguro-Receita (5%, ADCT art. 132, retido primeiro) e do CGIBS (art. 51 LC 227/2026, retido depois -- LC 227/2026 arts. 109-111 e 118 §§2º-4º). Mesmos parâmetros já publicados no Estudo 06, usados aqui só para o agregado nacional (aba 'Projeção IBS 2029-2033').</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
     </row>
@@ -2005,7 +2005,7 @@
     <row r="20" ht="45" customHeight="1">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>f_a (fração remanescente de ICMS+ISS) e s_a=1-f_a (fração já convertida em IBS) seguem o cronograma da transição constitucional (ADCT arts. 128 e 131, LC 227/2026). "IBS bruto" é a arrecadação total antes de qualquer dedução; a divisão entre critério histórico, critério destino, CGIBS e Seguro-Receita está na seção abaixo.</t>
+          <t>f_a (fração remanescente de ICMS+ISS) e s_a=1-f_a (fração já convertida em IBS) seguem o cronograma da transição constitucional (ADCT arts. 128 e 131, LC 227/2026). "IBS bruto" é a arrecadação total antes de qualquer dedução; a divisão entre critério histórico, critério destino, Seguro-Receita e CGIBS está na seção abaixo.</t>
         </is>
       </c>
     </row>
@@ -2081,15 +2081,15 @@
         <v/>
       </c>
       <c r="F24" s="9">
-        <f>G14*(1-B24)*C24</f>
+        <f>G14*(1-B24)*(1-D24)*C24</f>
         <v/>
       </c>
       <c r="G24" s="9">
-        <f>G14*(1-B24)*(1-C24)*D24</f>
+        <f>G14*(1-B24)*D24</f>
         <v/>
       </c>
       <c r="H24" s="9">
-        <f>G14*(1-B24)*(1-C24)*(1-D24)</f>
+        <f>G14*(1-B24)*(1-D24)*(1-C24)</f>
         <v/>
       </c>
       <c r="I24" s="9">
@@ -2115,15 +2115,15 @@
         <v/>
       </c>
       <c r="F25" s="9">
-        <f>G15*(1-B25)*C25</f>
+        <f>G15*(1-B25)*(1-D25)*C25</f>
         <v/>
       </c>
       <c r="G25" s="9">
-        <f>G15*(1-B25)*(1-C25)*D25</f>
+        <f>G15*(1-B25)*D25</f>
         <v/>
       </c>
       <c r="H25" s="9">
-        <f>G15*(1-B25)*(1-C25)*(1-D25)</f>
+        <f>G15*(1-B25)*(1-D25)*(1-C25)</f>
         <v/>
       </c>
       <c r="I25" s="9">
@@ -2149,15 +2149,15 @@
         <v/>
       </c>
       <c r="F26" s="9">
-        <f>G16*(1-B26)*C26</f>
+        <f>G16*(1-B26)*(1-D26)*C26</f>
         <v/>
       </c>
       <c r="G26" s="9">
-        <f>G16*(1-B26)*(1-C26)*D26</f>
+        <f>G16*(1-B26)*D26</f>
         <v/>
       </c>
       <c r="H26" s="9">
-        <f>G16*(1-B26)*(1-C26)*(1-D26)</f>
+        <f>G16*(1-B26)*(1-D26)*(1-C26)</f>
         <v/>
       </c>
       <c r="I26" s="9">
@@ -2183,15 +2183,15 @@
         <v/>
       </c>
       <c r="F27" s="9">
-        <f>G17*(1-B27)*C27</f>
+        <f>G17*(1-B27)*(1-D27)*C27</f>
         <v/>
       </c>
       <c r="G27" s="9">
-        <f>G17*(1-B27)*(1-C27)*D27</f>
+        <f>G17*(1-B27)*D27</f>
         <v/>
       </c>
       <c r="H27" s="9">
-        <f>G17*(1-B27)*(1-C27)*(1-D27)</f>
+        <f>G17*(1-B27)*(1-D27)*(1-C27)</f>
         <v/>
       </c>
       <c r="I27" s="9">
@@ -2217,15 +2217,15 @@
         <v/>
       </c>
       <c r="F28" s="9">
-        <f>G18*(1-B28)*C28</f>
+        <f>G18*(1-B28)*(1-D28)*C28</f>
         <v/>
       </c>
       <c r="G28" s="9">
-        <f>G18*(1-B28)*(1-C28)*D28</f>
+        <f>G18*(1-B28)*D28</f>
         <v/>
       </c>
       <c r="H28" s="9">
-        <f>G18*(1-B28)*(1-C28)*(1-D28)</f>
+        <f>G18*(1-B28)*(1-D28)*(1-C28)</f>
         <v/>
       </c>
       <c r="I28" s="9">
@@ -2236,7 +2236,7 @@
     <row r="30" ht="65" customHeight="1">
       <c r="A30" s="12" t="inlineStr">
         <is>
-          <t>alpha_a = fração do IBS bruto distribuída pelo critério histórico; (1-alpha_a) vai pelo critério destino, mas antes sofre duas deduções, nesta ordem: c_a (CGIBS, art. 51 LC 227/2026) e rho=5% (Seguro-Receita, ADCT art. 132). As quatro colunas de reais somam exatamente o IBS bruto do ano (coluna "Total" confere isso). alpha_a e c_a são os mesmos parâmetros já publicados no Estudo 06 (estudos/ibs-projecao-arrecadacao-br.html), usados aqui só para mostrar o tamanho de cada fatia no agregado nacional, sem entrar em qual estado ou município recebe o quê.</t>
+          <t>alpha_a = fração do IBS bruto distribuída pelo critério histórico; (1-alpha_a) vai pelo critério destino, mas antes sofre duas deduções, nesta ordem: rho=5% (Seguro-Receita, ADCT art. 132, art. 110 LC 227/2026 -- forma a Receita-Base do art. 111) e c_a (CGIBS, art. 51 e art. 118 §4º LC 227/2026, sobre a Receita-Base). As quatro colunas de reais somam exatamente o IBS bruto do ano (coluna "Total" confere isso). alpha_a e c_a são os mesmos parâmetros já publicados no Estudo 06 (estudos/ibs-projecao-arrecadacao-br.html), usados aqui só para mostrar o tamanho de cada fatia no agregado nacional, sem entrar em qual estado ou município recebe o quê.</t>
         </is>
       </c>
     </row>
